--- a/BAS/planningen&requirements/Suhailburndown_Bas .xlsx
+++ b/BAS/planningen&requirements/Suhailburndown_Bas .xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp2\htdocs\BAS\requirements\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp2\htdocs\startcode BAS\Planningen&amp;requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DED5A6F-97E1-498D-AD31-AD9215D6A237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{53B595D9-0D33-4DB6-89A5-0E7ADB641E05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D64FC014-072E-4862-83BE-4A77B874CE33}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>Taak</t>
   </si>
@@ -525,19 +525,19 @@
                   <c:v>47</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>47</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>47</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>47</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>47</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>47</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2058,9 +2058,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -2076,9 +2074,7 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -2108,8 +2104,8 @@
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
-        <v>32</v>
+      <c r="F15" s="2">
+        <v>3</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -2126,7 +2122,9 @@
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
+      <c r="F16" s="2">
+        <v>3</v>
+      </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -2142,7 +2140,9 @@
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="F17" s="2">
+        <v>3</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -2204,9 +2204,7 @@
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -2252,9 +2250,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="1"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -2659,36 +2655,36 @@
         <v>62</v>
       </c>
       <c r="C49" s="2">
-        <f t="shared" ref="C49:J49" si="0">B$49-SUM(C3:C48)</f>
+        <f>B$49-SUM(C3:C48)</f>
         <v>54</v>
       </c>
       <c r="D49" s="2">
-        <f t="shared" si="0"/>
+        <f>C$49-SUM(D3:D48)</f>
         <v>47</v>
       </c>
       <c r="E49" s="2">
-        <f t="shared" si="0"/>
+        <f>D$49-SUM(E3:E48)</f>
         <v>47</v>
       </c>
       <c r="F49" s="2">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f>E$49-SUM(F3:F48)</f>
+        <v>38</v>
       </c>
       <c r="G49" s="2">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f>F$49-SUM(G3:G48)</f>
+        <v>38</v>
       </c>
       <c r="H49" s="2">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f>G$49-SUM(H3:H48)</f>
+        <v>38</v>
       </c>
       <c r="I49" s="2">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f>H$49-SUM(I3:I48)</f>
+        <v>38</v>
       </c>
       <c r="J49" s="2">
-        <f t="shared" si="0"/>
-        <v>47</v>
+        <f>I$49-SUM(J3:J48)</f>
+        <v>38</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
@@ -2700,35 +2696,35 @@
         <v>62</v>
       </c>
       <c r="C50" s="8">
-        <f t="shared" ref="C50:J50" si="1">B$50-$B$50/COUNTA($C$1:$J$1)</f>
+        <f>B$50-$B$50/COUNTA($C$1:$J$1)</f>
         <v>54.25</v>
       </c>
       <c r="D50" s="8">
-        <f t="shared" si="1"/>
+        <f>C$50-$B$50/COUNTA($C$1:$J$1)</f>
         <v>46.5</v>
       </c>
       <c r="E50" s="8">
-        <f t="shared" si="1"/>
+        <f>D$50-$B$50/COUNTA($C$1:$J$1)</f>
         <v>38.75</v>
       </c>
       <c r="F50" s="8">
-        <f t="shared" si="1"/>
+        <f>E$50-$B$50/COUNTA($C$1:$J$1)</f>
         <v>31</v>
       </c>
       <c r="G50" s="8">
-        <f t="shared" si="1"/>
+        <f>F$50-$B$50/COUNTA($C$1:$J$1)</f>
         <v>23.25</v>
       </c>
       <c r="H50" s="8">
-        <f t="shared" si="1"/>
+        <f>G$50-$B$50/COUNTA($C$1:$J$1)</f>
         <v>15.5</v>
       </c>
       <c r="I50" s="8">
-        <f t="shared" si="1"/>
+        <f>H$50-$B$50/COUNTA($C$1:$J$1)</f>
         <v>7.75</v>
       </c>
       <c r="J50" s="8">
-        <f t="shared" si="1"/>
+        <f>I$50-$B$50/COUNTA($C$1:$J$1)</f>
         <v>0</v>
       </c>
     </row>
@@ -2741,15 +2737,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7EB66B5F93AD54F88C68A8B3F2870BB" ma:contentTypeVersion="17" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8c2a24a36bb82fd1af5ed8c009a064aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2982a79d-ff19-4d7a-967e-033e92b0df6e" xmlns:ns3="b123560b-c09d-4726-86a8-96759d196851" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c02a383944889dc160483fd1e510a099" ns2:_="" ns3:_="">
     <xsd:import namespace="2982a79d-ff19-4d7a-967e-033e92b0df6e"/>
@@ -2998,15 +2985,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E3F4124-1599-40F1-988E-E24419BF3D94}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3023,4 +3011,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC2C321F-7451-43AC-9409-3566FFDBBB5B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>